--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-ballot</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:44:45+00:00</t>
+    <t>2024-03-25T10:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:59:40+00:00</t>
+    <t>2024-03-25T11:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T08:02:06+00:00</t>
+    <t>2024-05-23T12:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:05:52+00:00</t>
+    <t>2024-05-23T12:32:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:32:02+00:00</t>
+    <t>2024-05-23T14:35:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T14:35:00+00:00</t>
+    <t>2024-06-11T15:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:12+00:00</t>
+    <t>2024-06-11T15:33:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:34+00:00</t>
+    <t>2024-07-02T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(WORK))</t>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-08T11:39:28+00:00</t>
+    <t>2024-07-17T12:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:13:27+00:00</t>
+    <t>2024-07-17T14:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T14:21:13+00:00</t>
+    <t>2024-07-17T15:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T15:15:49+00:00</t>
+    <t>2024-07-17T15:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T07:11:02+00:00</t>
+    <t>2024-07-25T15:28:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:28:42+00:00</t>
+    <t>2024-07-25T15:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:29:18+00:00</t>
+    <t>2024-07-25T15:44:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:44:10+00:00</t>
+    <t>2024-08-01T13:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0-ballot</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-03T15:38:30+00:00</t>
+    <t>2024-09-04T07:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T07:28:39+00:00</t>
+    <t>2024-09-04T07:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-06T12:53:53+00:00</t>
+    <t>2024-10-28T08:07:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -424,7 +424,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -444,7 +444,7 @@
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:07:18+00:00</t>
+    <t>2024-10-28T08:08:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:08:30+00:00</t>
+    <t>2024-10-29T10:42:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:05:50+00:00</t>
+    <t>2025-01-28T09:07:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:07:36+00:00</t>
+    <t>2025-02-04T08:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T08:51:44+00:00</t>
+    <t>2025-02-04T09:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T09:30:35+00:00</t>
+    <t>2025-02-19T13:47:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:47:59+00:00</t>
+    <t>2025-02-19T13:52:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:52:01+00:00</t>
+    <t>2025-02-19T13:53:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2062" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2062" uniqueCount="433">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:53:58+00:00</t>
+    <t>2025-02-19T13:58:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -638,6 +638,11 @@
     <t>FR Core Organization Short Name Extension</t>
   </si>
   <si>
+    <t>Libellé court de l'organisation
++The Organization short name</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
@@ -655,6 +660,10 @@
     <t>FR Core Organization Description Extension</t>
   </si>
   <si>
+    <t>Description textuelle d'une organisation
+Organization description</t>
+  </si>
+  <si>
     <t>Organization.extension:budgetLetter</t>
   </si>
   <si>
@@ -668,7 +677,8 @@
     <t>FR Core Organization Budget Letter Extension</t>
   </si>
   <si>
-    <t>An organization budget letter | Lettre budgétaire de l'UF</t>
+    <t>Lettre budgétaire de l'UF
+An organization budget letter</t>
   </si>
   <si>
     <t>Organization.extension:equipmentField</t>
@@ -684,7 +694,9 @@
     <t>FR Core Organization Field Extension</t>
   </si>
   <si>
-    <t>Equipment field | Discipline d'équipement</t>
+    <t>Discipline d'équipement
++Equipment field</t>
   </si>
   <si>
     <t>Organization.extension:activityField</t>
@@ -700,7 +712,8 @@
     <t>FR Core Organization Activity Field Extension</t>
   </si>
   <si>
-    <t>Activity field of an organization | Champ d'activité d'une UF</t>
+    <t>Champ d'activité d'une UF.
+Activity field of an organization</t>
   </si>
   <si>
     <t>Organization.extension:external</t>
@@ -716,7 +729,9 @@
     <t>FR Core Organization External Extension</t>
   </si>
   <si>
-    <t>External ward of the facility | UF externe à l'établissement</t>
+    <t>UF externe à l'établissement.
++External ward of the facility</t>
   </si>
   <si>
     <t>Organization.extension:accomodationSpace</t>
@@ -732,7 +747,9 @@
     <t>FR Core Organization Total Number Of Theorical Accomodation Space Extension</t>
   </si>
   <si>
-    <t>Total number of theorical accomodation space | Nombre total de places d'hébergement théoriques</t>
+    <t>Nombre total de places d'hébergement théoriques
++Total number of theorical accomodation space</t>
   </si>
   <si>
     <t>Organization.extension:applicantAct</t>
@@ -748,7 +765,8 @@
     <t>FR Core Organization Applicant Act Extension</t>
   </si>
   <si>
-    <t>An organization that asks soma acts | UF demandeuse d'actes</t>
+    <t>UF demandeuse d'actes
+An organization that asks soma acts</t>
   </si>
   <si>
     <t>Organization.extension:executantAct</t>
@@ -764,7 +782,9 @@
     <t>FR Core Organization Executant Extension</t>
   </si>
   <si>
-    <t>An executant act organization | Une UF exécutante d'actes</t>
+    <t>Une UF exécutante d'actes
++An executant act organization</t>
   </si>
   <si>
     <t>Organization.extension:analysisSection</t>
@@ -780,7 +800,8 @@
     <t>FR Core Organization Analysis Section Extension</t>
   </si>
   <si>
-    <t>an oraganization analysis section | Section d'analyse d'une UF</t>
+    <t>Section d'analyse d'une UF.
+An oraganization analysis section</t>
   </si>
   <si>
     <t>Organization.extension:activityType</t>
@@ -796,7 +817,8 @@
     <t>FR Core Organization Activity Type Extension</t>
   </si>
   <si>
-    <t>An organization activity type | type d'activité d'une UF</t>
+    <t>Type d'activité d'une UF
+An organization activity type</t>
   </si>
   <si>
     <t>Organization.extension:usePeriod</t>
@@ -3805,7 +3827,7 @@
         <v>199</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3865,7 +3887,7 @@
         <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>117</v>
@@ -3885,13 +3907,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>78</v>
@@ -3913,13 +3935,13 @@
         <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3979,7 +4001,7 @@
         <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>117</v>
@@ -3999,13 +4021,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>78</v>
@@ -4027,13 +4049,13 @@
         <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4093,7 +4115,7 @@
         <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>117</v>
@@ -4113,13 +4135,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>78</v>
@@ -4141,13 +4163,13 @@
         <v>78</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4207,7 +4229,7 @@
         <v>80</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>117</v>
@@ -4227,13 +4249,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>78</v>
@@ -4255,13 +4277,13 @@
         <v>78</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4321,7 +4343,7 @@
         <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>117</v>
@@ -4341,13 +4363,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>78</v>
@@ -4369,13 +4391,13 @@
         <v>78</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4435,7 +4457,7 @@
         <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>117</v>
@@ -4455,13 +4477,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>78</v>
@@ -4483,13 +4505,13 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4549,7 +4571,7 @@
         <v>80</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>117</v>
@@ -4569,13 +4591,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>78</v>
@@ -4597,13 +4619,13 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4663,7 +4685,7 @@
         <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>117</v>
@@ -4683,13 +4705,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>78</v>
@@ -4711,13 +4733,13 @@
         <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4777,7 +4799,7 @@
         <v>80</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>117</v>
@@ -4797,13 +4819,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>78</v>
@@ -4825,13 +4847,13 @@
         <v>78</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4891,7 +4913,7 @@
         <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>117</v>
@@ -4911,13 +4933,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>78</v>
@@ -4939,13 +4961,13 @@
         <v>78</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5005,7 +5027,7 @@
         <v>80</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>117</v>
@@ -5025,13 +5047,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>78</v>
@@ -5053,13 +5075,13 @@
         <v>78</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="L30" t="s" s="2">
         <v>193</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5139,10 +5161,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5168,16 +5190,16 @@
         <v>109</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N31" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>78</v>
@@ -5226,7 +5248,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5255,10 +5277,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5281,17 +5303,17 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>78</v>
@@ -5340,7 +5362,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5349,30 +5371,30 @@
         <v>80</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5481,10 +5503,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5595,10 +5617,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5624,16 +5646,16 @@
         <v>168</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -5658,11 +5680,11 @@
         <v>78</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>78</v>
@@ -5680,7 +5702,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5698,7 +5720,7 @@
         <v>191</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>78</v>
@@ -5709,10 +5731,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5735,19 +5757,19 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -5776,7 +5798,7 @@
       </c>
       <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>78</v>
@@ -5794,7 +5816,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5809,10 +5831,10 @@
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>78</v>
@@ -5823,10 +5845,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5852,16 +5874,16 @@
         <v>130</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -5874,7 +5896,7 @@
         <v>78</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>78</v>
@@ -5910,7 +5932,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5925,13 +5947,13 @@
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -5939,10 +5961,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5968,13 +5990,13 @@
         <v>102</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5988,7 +6010,7 @@
         <v>78</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>78</v>
@@ -6024,7 +6046,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6039,13 +6061,13 @@
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>78</v>
@@ -6053,10 +6075,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6079,13 +6101,13 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6136,7 +6158,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6151,13 +6173,13 @@
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>78</v>
@@ -6165,10 +6187,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6191,16 +6213,16 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6250,7 +6272,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6265,13 +6287,13 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>78</v>
@@ -6279,10 +6301,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6305,70 +6327,70 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="P41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q41" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="R41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF41" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="P41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q41" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="R41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6383,24 +6405,24 @@
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6423,19 +6445,19 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -6464,7 +6486,7 @@
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>78</v>
@@ -6482,7 +6504,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6497,24 +6519,24 @@
         <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6540,16 +6562,16 @@
         <v>102</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>78</v>
@@ -6598,7 +6620,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6607,19 +6629,19 @@
         <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>78</v>
@@ -6627,10 +6649,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6656,16 +6678,16 @@
         <v>102</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -6714,7 +6736,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6732,7 +6754,7 @@
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
@@ -6743,10 +6765,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6769,19 +6791,19 @@
         <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>78</v>
@@ -6830,7 +6852,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6839,19 +6861,19 @@
         <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>78</v>
@@ -6859,10 +6881,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6885,19 +6907,19 @@
         <v>78</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>78</v>
@@ -6946,7 +6968,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6955,19 +6977,19 @@
         <v>80</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>78</v>
@@ -6975,10 +6997,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7001,17 +7023,17 @@
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>78</v>
@@ -7060,7 +7082,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7075,10 +7097,10 @@
         <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>106</v>
@@ -7089,10 +7111,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7115,19 +7137,19 @@
         <v>78</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>78</v>
@@ -7176,7 +7198,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7194,7 +7216,7 @@
         <v>78</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
@@ -7205,10 +7227,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7317,10 +7339,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7431,14 +7453,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7460,16 +7482,16 @@
         <v>109</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>78</v>
@@ -7518,7 +7540,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7547,10 +7569,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7573,17 +7595,17 @@
         <v>78</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>78</v>
@@ -7611,10 +7633,10 @@
         <v>150</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>78</v>
@@ -7632,7 +7654,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7650,7 +7672,7 @@
         <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>78</v>
@@ -7661,10 +7683,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7687,17 +7709,17 @@
         <v>78</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -7746,7 +7768,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7761,10 +7783,10 @@
         <v>100</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>78</v>
@@ -7775,10 +7797,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7801,17 +7823,17 @@
         <v>78</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>78</v>
@@ -7860,7 +7882,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7875,10 +7897,10 @@
         <v>100</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>78</v>
@@ -7889,10 +7911,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7915,17 +7937,17 @@
         <v>78</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -7974,7 +7996,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -7989,10 +8011,10 @@
         <v>100</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>78</v>
@@ -8003,10 +8025,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8029,17 +8051,17 @@
         <v>78</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -8088,7 +8110,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:58:46+00:00</t>
+    <t>2025-02-19T14:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T14:07:54+00:00</t>
+    <t>2025-02-19T14:26:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:11:18+00:00</t>
+    <t>2025-05-20T13:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:27:17+00:00</t>
+    <t>2025-05-20T13:29:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:29:42+00:00</t>
+    <t>2025-05-20T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:48:39+00:00</t>
+    <t>2025-06-04T13:32:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -827,7 +827,7 @@
     <t>usePeriod</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {organization-period}
+    <t xml:space="preserve">Extension {organization-period|5.2.0}
 </t>
   </si>
   <si>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-04T13:32:30+00:00</t>
+    <t>2025-06-24T17:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T17:01:22+00:00</t>
+    <t>2025-07-04T12:19:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T12:19:33+00:00</t>
+    <t>2025-07-08T13:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-08T13:28:39+00:00</t>
+    <t>2025-07-16T09:34:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T09:34:35+00:00</t>
+    <t>2025-07-30T14:55:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-30T14:55:53+00:00</t>
+    <t>2025-10-08T07:32:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -827,7 +827,7 @@
     <t>usePeriod</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {organization-period|5.2.0}
+    <t xml:space="preserve">Extension {organization-period|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
@@ -5141,7 +5141,7 @@
         <v>80</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>78</v>
+        <v>201</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>117</v>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T07:32:57+00:00</t>
+    <t>2025-10-08T12:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T12:04:30+00:00</t>
+    <t>2025-10-08T16:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:25:45+00:00</t>
+    <t>2026-02-04T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T13:09:39+00:00</t>
+    <t>2026-02-09T06:47:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T06:47:58+00:00</t>
+    <t>2026-02-11T16:15:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -695,10 +695,10 @@
     <t>closureReason</t>
   </si>
   <si>
-    <t>Organization.extension:members</t>
-  </si>
-  <si>
-    <t>members</t>
+    <t>Organization.extension:member</t>
+  </si>
+  <si>
+    <t>member</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-member|2.2.0-ballot-2}

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T16:15:37+00:00</t>
+    <t>2026-02-17T10:02:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T10:02:14+00:00</t>
+    <t>2026-02-23T09:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T09:26:22+00:00</t>
+    <t>2026-02-23T10:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T10:39:10+00:00</t>
+    <t>2026-02-23T12:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T07:09:47+00:00</t>
+    <t>2026-03-25T10:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:11+00:00</t>
+    <t>2026-03-25T10:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:40+00:00</t>
+    <t>2026-03-25T10:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:25:13+00:00</t>
+    <t>2026-03-25T15:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T15:00:47+00:00</t>
+    <t>2026-03-31T09:16:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2063" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2064" uniqueCount="411">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T09:16:18+00:00</t>
+    <t>2026-05-07T06:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -650,14 +650,18 @@
     <t>description</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-Organization.description}
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-Organization.description|0.1.0}
 </t>
   </si>
   <si>
-    <t>Optional Extensions Element</t>
-  </si>
-  <si>
-    <t>Optional Extension Element - found in all resources.</t>
+    <t>R5: Additional details about the Organization that could be displayed as further information to identify the Organization beyond its name (new)</t>
+  </si>
+  <si>
+    <t>R5: `Organization.description` (new:markdown)</t>
+  </si>
+  <si>
+    <t>Element `Organization.description` has a context of Organization based on following the parent source element upwards and mapping to `Organization`.
+Element `Organization.description` has no mapping targets in FHIR R4. Typically, this is because the element has been added (is a new element).</t>
   </si>
   <si>
     <t>Organization.extension:usePeriod</t>
@@ -3866,7 +3870,9 @@
       <c r="M20" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="N20" s="2"/>
+      <c r="N20" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>78</v>
@@ -3933,7 +3939,7 @@
         <v>78</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>78</v>
@@ -3944,13 +3950,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>78</v>
@@ -3972,13 +3978,13 @@
         <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>193</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4058,13 +4064,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>78</v>
@@ -4086,16 +4092,16 @@
         <v>78</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4174,13 +4180,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>78</v>
@@ -4202,16 +4208,16 @@
         <v>78</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4290,13 +4296,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>78</v>
@@ -4318,13 +4324,13 @@
         <v>78</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4404,13 +4410,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>78</v>
@@ -4432,13 +4438,13 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4518,13 +4524,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>78</v>
@@ -4546,13 +4552,13 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4632,13 +4638,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>78</v>
@@ -4660,13 +4666,13 @@
         <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4746,13 +4752,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>78</v>
@@ -4774,13 +4780,13 @@
         <v>78</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4860,13 +4866,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>78</v>
@@ -4888,13 +4894,13 @@
         <v>78</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4974,13 +4980,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>78</v>
@@ -5002,13 +5008,13 @@
         <v>78</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5088,13 +5094,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>78</v>
@@ -5116,13 +5122,13 @@
         <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5202,13 +5208,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>78</v>
@@ -5230,13 +5236,13 @@
         <v>78</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5316,10 +5322,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5345,16 +5351,16 @@
         <v>109</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -5403,7 +5409,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5432,10 +5438,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5458,17 +5464,17 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>78</v>
@@ -5517,7 +5523,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5526,30 +5532,30 @@
         <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5572,70 +5578,70 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="P35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q35" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="R35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="L35" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="P35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q35" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="R35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5650,24 +5656,24 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5690,26 +5696,26 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>78</v>
@@ -5731,7 +5737,7 @@
       </c>
       <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>78</v>
@@ -5749,7 +5755,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5764,24 +5770,24 @@
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5807,16 +5813,16 @@
         <v>102</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -5865,7 +5871,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5874,19 +5880,19 @@
         <v>88</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -5894,10 +5900,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5923,16 +5929,16 @@
         <v>102</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -5981,7 +5987,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -5999,7 +6005,7 @@
         <v>78</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>78</v>
@@ -6010,10 +6016,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6036,19 +6042,19 @@
         <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>78</v>
@@ -6097,7 +6103,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6106,19 +6112,19 @@
         <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>78</v>
@@ -6126,10 +6132,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6152,19 +6158,19 @@
         <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>78</v>
@@ -6213,7 +6219,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6222,19 +6228,19 @@
         <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>78</v>
@@ -6242,10 +6248,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6268,17 +6274,17 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>78</v>
@@ -6327,7 +6333,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6342,10 +6348,10 @@
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>106</v>
@@ -6356,10 +6362,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6468,10 +6474,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6582,10 +6588,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6611,13 +6617,13 @@
         <v>102</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6667,7 +6673,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6676,7 +6682,7 @@
         <v>88</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>100</v>
@@ -6696,10 +6702,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6725,13 +6731,13 @@
         <v>130</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6761,7 +6767,7 @@
       </c>
       <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>78</v>
@@ -6779,7 +6785,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6808,10 +6814,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6834,16 +6840,16 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6893,7 +6899,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6911,7 +6917,7 @@
         <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>78</v>
@@ -6922,10 +6928,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6951,13 +6957,13 @@
         <v>102</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7007,7 +7013,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7036,10 +7042,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7062,19 +7068,19 @@
         <v>78</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>78</v>
@@ -7123,7 +7129,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7141,7 +7147,7 @@
         <v>78</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
@@ -7152,10 +7158,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7264,10 +7270,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7378,14 +7384,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7407,16 +7413,16 @@
         <v>109</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>78</v>
@@ -7465,7 +7471,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7494,10 +7500,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7520,17 +7526,17 @@
         <v>78</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>78</v>
@@ -7558,10 +7564,10 @@
         <v>150</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>78</v>
@@ -7579,7 +7585,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7597,7 +7603,7 @@
         <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>78</v>
@@ -7608,10 +7614,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7634,17 +7640,17 @@
         <v>78</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -7693,7 +7699,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7708,10 +7714,10 @@
         <v>100</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>78</v>
@@ -7722,10 +7728,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7748,17 +7754,17 @@
         <v>78</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>78</v>
@@ -7807,7 +7813,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7822,10 +7828,10 @@
         <v>100</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>78</v>
@@ -7836,10 +7842,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7862,17 +7868,17 @@
         <v>78</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -7921,7 +7927,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -7936,10 +7942,10 @@
         <v>100</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>78</v>
@@ -7950,10 +7956,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7976,17 +7982,17 @@
         <v>78</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -8035,7 +8041,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:50:40+00:00</t>
+    <t>2026-05-27T14:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:53:55+00:00</t>
+    <t>2026-05-28T14:22:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:22:24+00:00</t>
+    <t>2026-06-12T14:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:04:24+00:00</t>
+    <t>2026-06-12T14:05:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,7 +269,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}org-1:The organization SHALL at least have a name or an identifier, and possibly more than one {(identifier.count() + name.count()) &gt; 0}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}org-1:The organization SHALL at least have a name or an identifier, and possibly more than one {(identifier.count() + name.count()) &gt; 0}name-or-identifier:identifier or name SHALL be present {identifier.exists() or name.exists()}</t>
   </si>
   <si>
     <t>(also see master files messages)</t>
@@ -866,7 +866,7 @@
 </t>
   </si>
   <si>
-    <t>Identifies this organization  across multiple systems</t>
+    <t>Organization business identifier</t>
   </si>
   <si>
     <t>Identifier for the organization that is used to identify the organization across multiple disparate systems.</t>
@@ -933,7 +933,7 @@
 </t>
   </si>
   <si>
-    <t>Kind of organization</t>
+    <t>Organization type</t>
   </si>
   <si>
     <t>The kind(s) of organization that this is.</t>
@@ -970,7 +970,7 @@
     <t>Organization.name</t>
   </si>
   <si>
-    <t>Name used for the organization</t>
+    <t>Name of the organization</t>
   </si>
   <si>
     <t>A name associated with the organization.</t>
@@ -1014,7 +1014,7 @@
 </t>
   </si>
   <si>
-    <t>A contact detail for the organization</t>
+    <t>Organization telecom</t>
   </si>
   <si>
     <t>A contact detail for the organization.</t>
@@ -1086,7 +1086,7 @@
 </t>
   </si>
   <si>
-    <t>The organization of which this organization forms a part</t>
+    <t>The organization of which this organization is part of: e.g. an ERN</t>
   </si>
   <si>
     <t>The organization of which this organization forms a part.</t>
@@ -1182,7 +1182,7 @@
 </t>
   </si>
   <si>
-    <t>Contact for the organization for a certain purpose</t>
+    <t>Organization contact infos</t>
   </si>
   <si>
     <t>Contact for the organization for a certain purpose.</t>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>88</v>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:05:00+00:00</t>
+    <t>2026-06-12T14:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:35:23+00:00</t>
+    <t>2026-06-26T12:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T12:32:04+00:00</t>
+    <t>2026-06-29T09:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T09:30:52+00:00</t>
+    <t>2026-07-22T12:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:21:07+00:00</t>
+    <t>2026-07-27T15:02:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:02:31+00:00</t>
+    <t>2026-08-03T12:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T12:52:25+00:00</t>
+    <t>2026-08-04T12:22:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:22:31+00:00</t>
+    <t>2026-08-04T12:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:29:23+00:00</t>
+    <t>2026-08-10T16:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
